--- a/public/datos/3.3_Matriz_indicadores.xlsx
+++ b/public/datos/3.3_Matriz_indicadores.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Indicadores" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Reglas_Semaforo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Enunciado_Caso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Reglas_Tolerancia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Matriz_Semaforo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,185 +427,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Indicador</t>
+          <t>Sección</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Fórmula</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Meta (%)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Resultado (%)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Semáforo</t>
+          <t>Detalle del Requerimiento / Parámetros del Caso</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Documentos vigentes</t>
+          <t>Código de Actividad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Documentos vigentes / Total de documentos × 100</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>90</v>
-      </c>
-      <c r="D2" t="n">
-        <v>80</v>
+          <t>3.3</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Satisfacción del cliente</t>
+          <t>Título del Caso</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Clientes satisfechos / Clientes encuestados × 100</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>85</v>
-      </c>
-      <c r="D3" t="n">
-        <v>88</v>
+          <t>Matriz de indicadores y semaforización dinámica de metas</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cumplimiento del plan de auditorías</t>
+          <t>Organización</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Auditorías realizadas / Auditorías programadas × 100</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>95</v>
+          <t>Lácteos del Caribe S.A.S. - Sistema Integrado de Gestión</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Acciones correctivas cerradas a tiempo</t>
+          <t>1. Situación Problema</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Acciones cerradas a tiempo / Acciones abiertas × 100</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>80</v>
-      </c>
-      <c r="D5" t="n">
-        <v>70</v>
+          <t>Los 8 procesos reportaron resultados frente a sus metas operativas. Se requiere una matriz que califique automáticamente la eficacia y semaforice las desviaciones.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cumplimiento del plan de capacitación</t>
+          <t>2. Misión del Aprendiz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capacitaciones realizadas / Capacitaciones programadas × 100</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>90</v>
-      </c>
-      <c r="D6" t="n">
-        <v>92</v>
+          <t>Estructurar la matriz de indicadores calculando la brecha (Resultado - Meta), evaluando el estado cualitativo con SI anidado y aplicando formato condicional de 3 semáforos.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Entregas a tiempo</t>
+          <t>Requerimiento 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pedidos entregados a tiempo / Pedidos totales × 100</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>95</v>
-      </c>
-      <c r="D7" t="n">
-        <v>96</v>
+          <t>Cálculo de la Brecha: =Resultado - Meta (muestra la desviación matemática frente a la meta corporativa).</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Proveedores evaluados</t>
+          <t>Requerimiento 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Proveedores evaluados / Proveedores activos × 100</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>100</v>
-      </c>
-      <c r="D8" t="n">
-        <v>85</v>
+          <t>Estado Cualitativo con SI anidado: si Resultado &gt;= Meta -&gt; 'Conforme'; si Resultado &gt;= Meta - 10 -&gt; 'En Observación'; de lo contrario -&gt; 'Crítico'.</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mantenimientos preventivos ejecutados</t>
+          <t>Requerimiento 3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mantenimientos ejecutados / Mantenimientos programados × 100</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>90</v>
-      </c>
-      <c r="D9" t="n">
-        <v>70</v>
+          <t>Semáforo Condicional: Aplicar formato condicional: Verde (Conforme), Amarillo (En Observación) y Rojo (Crítico).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Requerimiento 4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Alerta CAPA: Resaltar en negrita y rojo los indicadores en estado Crítico que requieran plan de acción correctiva inmediato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Dificultad Clave / Regla Técnica</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cada indicador tiene una meta distinta (80%, 90%, 95%, 100%). No compares contra un número fijo: las fórmulas condicionales deben comparar celdas relativas (Resultado vs Meta).</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -618,59 +577,351 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Nivel de Estado</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Condición</t>
+          <t>Condición Matemática</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Acción Requerida</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Color del Semáforo</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Resultado ≥ Meta</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Mantener seguimiento regular</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Verde</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Resultado ≥ Meta</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>En Observación</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Meta - 10 ≤ Resultado &lt; Meta</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Revisión en comité de proceso</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Amarillo</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Meta - 10 ≤ Resultado &lt; Meta</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Resultado &lt; Meta - 10</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apertura obligatoria de Acción Correctiva (CAPA)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Rojo</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Proceso</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Meta (%)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Resultado Real (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Brecha (Resultado - Meta)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Estado Cualitativo (=SI)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Semáforo (Formato Condicional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>IND-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Documentos vigentes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Gestión de la calidad</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>90</v>
+      </c>
+      <c r="E2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>IND-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Satisfacción del cliente</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Comercial y ventas</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>85</v>
+      </c>
+      <c r="E3" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>IND-03</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Resultado &lt; Meta - 10</t>
-        </is>
+          <t>Cumplimiento del plan de auditorías</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Gestión de la calidad</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>IND-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Acciones correctivas cerradas a tiempo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Gestión de la calidad</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>80</v>
+      </c>
+      <c r="E5" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>IND-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cumplimiento del plan de capacitación</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Talento humano</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>90</v>
+      </c>
+      <c r="E6" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IND-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Entregas a tiempo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Logística y distribución</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>95</v>
+      </c>
+      <c r="E7" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>IND-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Proveedores evaluados</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Compras</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IND-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mantenimientos preventivos ejecutados</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>90</v>
+      </c>
+      <c r="E9" t="n">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
